--- a/results/Int Task Remove ACC 0.7/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.7/Linea_fi_all.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.031630648330058984 +/- 0.002467555341273174</t>
+          <t>-0.031679764243614975 +/- 0.0024286316925493374</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.08560042507970239 +/- 0.0043261780593698</t>
+          <t>0.08565356004250792 +/- 0.004275961644788683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.07242295430393193 +/- 0.003460306090364484</t>
+          <t>0.07252922422954297 +/- 0.0034700832874082154</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.11137088204038252 +/- 0.003233820202912409</t>
+          <t>0.11126461211477148 +/- 0.00327718256006572</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.020454545454545482 +/- 0.0031185244739247876</t>
+          <t>-0.02050395256916998 +/- 0.0030235378025285026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.0004940711462450897 +/- 0.0009374340889827156</t>
+          <t>-0.00044466403162057855 +/- 0.0009991970561342247</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0008844665561083542 +/- 0.000442233278054191</t>
+          <t>0.0008844665561083653 +/- 0.0005066418678779576</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.0009397457158651368 +/- 0.0004975124378109751</t>
+          <t>0.0007739082365948002 +/- 0.0003666804632786495</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.03313735970069478 +/- 0.0017726482043588438</t>
+          <t>0.033190807055050744 +/- 0.001714485829219176</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
